--- a/TestCase_VINAGO_SanPham_TiengViet_Full.xlsx
+++ b/TestCase_VINAGO_SanPham_TiengViet_Full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java lean\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B1542-FEB8-4275-96B5-F50CAE5E1266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A7151C-42FA-4E8E-B171-0C1EAEBB9486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="243">
-  <si>
-    <t>BỘ TEST CASE – APP VINAGO (MODULE SẢN PHẨM) (Cập nhật Server &amp; Thiết bị)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="236">
   <si>
     <t>Mã TC</t>
   </si>
@@ -54,9 +51,6 @@
   </si>
   <si>
     <t>Ưu tiên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  NHÓM 1: CẤU TRÚC DANH MỤC &amp; SẢN PHẨM</t>
   </si>
   <si>
     <t>TC_SP_001</t>
@@ -268,9 +262,6 @@
     <t>- App hiển thị thông tin đúng 3 mức giá combo khi đạt số lượng yêu cầu.</t>
   </si>
   <si>
-    <t xml:space="preserve">  NHÓM 2: ẨN/HIỆN DANH MỤC SẢN PHẨM</t>
-  </si>
-  <si>
     <t>TC_SP_012</t>
   </si>
   <si>
@@ -351,9 +342,6 @@
     <t>- SKU1 không hiển thị trong danh sách sản phẩm.</t>
   </si>
   <si>
-    <t xml:space="preserve">  NHÓM 3: ẨN/HIỆN THEO ĐỐI TƯỢNG</t>
-  </si>
-  <si>
     <t>TC_SP_017</t>
   </si>
   <si>
@@ -513,9 +501,6 @@
     <t>Thấp</t>
   </si>
   <si>
-    <t xml:space="preserve">  NHÓM 4: SẢN PHẨM BÁN CHẠY &amp; MỚI</t>
-  </si>
-  <si>
     <t>TC_SP_026</t>
   </si>
   <si>
@@ -606,9 +591,6 @@
 - KHÔNG hiển thị Số lượng đã bán và Đánh giá sao.</t>
   </si>
   <si>
-    <t xml:space="preserve">  NHÓM 5: SP TƯƠNG QUAN &amp; KHÔNG HOA HỒNG</t>
-  </si>
-  <si>
     <t>TC_SP_031</t>
   </si>
   <si>
@@ -682,9 +664,6 @@
   <si>
     <t>- Danh sách tự động cập nhật đúng ngày giờ hẹn.
 - Xóa danh sách cũ / thay bằng danh sách mới theo cấu hình.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  NHÓM 6: GIAO DIỆN APP</t>
   </si>
   <si>
     <t>TC_SP_035</t>
@@ -809,7 +788,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,19 +798,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -887,7 +854,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -897,11 +864,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
@@ -950,7 +912,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -973,114 +935,92 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF595959"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF595959"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF595959"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF595959"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1384,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1399,1557 +1339,1443 @@
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-    </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H4" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>18</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="9" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="D9" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>26</v>
+      <c r="I9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>20</v>
+        <v>235</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H12" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>20</v>
+        <v>71</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>28</v>
+      <c r="A13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>26</v>
+        <v>230</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H14" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
+      <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H17" s="7" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>14</v>
+      <c r="A19" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>20</v>
+        <v>235</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H21" s="7" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="I21" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
+      <c r="C22" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>28</v>
+      <c r="A24" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>107</v>
+        <v>230</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>135</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>28</v>
+      <c r="A25" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>26</v>
+        <v>230</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>20</v>
+        <v>145</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H27" s="7" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>28</v>
+        <v>148</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>20</v>
+        <v>157</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="A30" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>144</v>
+      <c r="H31" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>28</v>
+        <v>175</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
+        <v>179</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="J34" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H35" s="7" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>20</v>
+        <v>196</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H36" s="7" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>26</v>
+        <v>202</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>28</v>
+        <v>198</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>28</v>
+      <c r="A38" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>173</v>
+        <v>230</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>212</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>164</v>
+      <c r="A39" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>198</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="J39" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-    </row>
-    <row r="42" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C42" s="4" t="s">
+      <c r="H40" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F44" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="H44" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I44" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="J44" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-    </row>
-    <row r="48" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F51" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="H51" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="I51" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="J51" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="H41" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="I41" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52" s="7" t="s">
+      <c r="J41" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I52" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>20</v>
+      <c r="K41" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="7">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A47:K47"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2958,13 +2784,13 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D14 D17:D21 D24:D32 D35:D39 D42:D45 D48:D53</xm:sqref>
+          <xm:sqref>D2:D12 D13:D17 D18:D26 D27:D31 D32:D35 D36:D41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AE66B974-2160-421A-8E70-060DEBFBAE8C}">
           <x14:formula1>
             <xm:f>Sheet1!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E14 E17:E21 E48:E53 E35:E39 E42:E45 E24:E32</xm:sqref>
+          <xm:sqref>E2:E12 E13:E17 E36:E41 E27:E31 E32:E35 E18:E26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2982,34 +2808,34 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
